--- a/data/trans_orig/P15A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>21244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>13095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>32452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452187</t>
+          <t>452532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466668</t>
+          <t>467167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290761</t>
+          <t>290818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>302909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>748290</t>
+          <t>748005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767983</t>
+          <t>767362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22903</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29920</t>
+          <t>30050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344031</t>
+          <t>342773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359579</t>
+          <t>359397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359267</t>
+          <t>359105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369877</t>
+          <t>369818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708879</t>
+          <t>708749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727456</t>
+          <t>727492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19301</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41758</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46761</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>500631</t>
+          <t>501644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523088</t>
+          <t>523483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157007</t>
+          <t>157321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165990</t>
+          <t>166020</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663410</t>
+          <t>662845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686939</t>
+          <t>686691</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26935</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51898</t>
+          <t>53219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48701</t>
+          <t>49402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82020</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1186436</t>
+          <t>1185115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1211399</t>
+          <t>1210909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>676174</t>
+          <t>677801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697701</t>
+          <t>697632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870600</t>
+          <t>1871501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903919</t>
+          <t>1903218</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21388</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33869</t>
+          <t>32254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48655</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>329167</t>
+          <t>329208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343382</t>
+          <t>343817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534883</t>
+          <t>536498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>554076</t>
+          <t>554352</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>870652</t>
+          <t>871464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>894450</t>
+          <t>894511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19469</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>40836</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57493</t>
+          <t>59122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272332</t>
+          <t>272128</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288353</t>
+          <t>288352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1208528</t>
+          <t>1207924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1229291</t>
+          <t>1230397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1489467</t>
+          <t>1487838</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1514845</t>
+          <t>1514663</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102351</t>
+          <t>102509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145658</t>
+          <t>146844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74598</t>
+          <t>76539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>112575</t>
+          <t>115494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>188744</t>
+          <t>186866</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248000</t>
+          <t>244476</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3124532</t>
+          <t>3123346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3167839</t>
+          <t>3167681</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3265549</t>
+          <t>3262630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3303526</t>
+          <t>3301585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6400314</t>
+          <t>6403838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6459570</t>
+          <t>6461448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35184</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413353</t>
+          <t>411323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429898</t>
+          <t>429568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296390</t>
+          <t>296192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310846</t>
+          <t>311635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>716481</t>
+          <t>715950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737749</t>
+          <t>737989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>19298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11778</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>25561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>398683</t>
+          <t>399499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412694</t>
+          <t>412535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326233</t>
+          <t>327236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337030</t>
+          <t>337040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730784</t>
+          <t>731247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747718</t>
+          <t>747875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>12918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14642</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>34281</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>601161</t>
+          <t>602616</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620052</t>
+          <t>619588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247156</t>
+          <t>247211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258146</t>
+          <t>258098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853827</t>
+          <t>855263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>874902</t>
+          <t>874998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24347</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>26983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>38157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>68389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1110965</t>
+          <t>1109624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134662</t>
+          <t>1134991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>739747</t>
+          <t>739674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>756762</t>
+          <t>757150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857962</t>
+          <t>1857278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886970</t>
+          <t>1887510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>22775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27692</t>
+          <t>27996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53597</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>487914</t>
+          <t>487821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>503727</t>
+          <t>502843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>723647</t>
+          <t>723572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744323</t>
+          <t>743884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1218521</t>
+          <t>1218874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1244426</t>
+          <t>1244122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,49 +5098,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>37885</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>27166</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>52671</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>4,75%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>37885</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>27246</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>51423</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32386</t>
+          <t>34032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>58602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254195</t>
+          <t>253082</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263972</t>
+          <t>264001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,47 +5211,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1071466</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1056680</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1082185</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>95,25%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1008</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1071466</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1057928</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1082105</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1315641</t>
+          <t>1317631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1343847</t>
+          <t>1342201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>78337</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118978</t>
+          <t>119118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79383</t>
+          <t>79636</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120371</t>
+          <t>121801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169743</t>
+          <t>170310</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226057</t>
+          <t>228484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3302932</t>
+          <t>3302792</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3342525</t>
+          <t>3343573</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3429754</t>
+          <t>3428324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3470742</t>
+          <t>3470489</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6745978</t>
+          <t>6743551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6802292</t>
+          <t>6801725</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25901</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410466</t>
+          <t>410822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425155</t>
+          <t>424892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333451</t>
+          <t>333363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>750246</t>
+          <t>749029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766994</t>
+          <t>766950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365192</t>
+          <t>364870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375196</t>
+          <t>375250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350313</t>
+          <t>350551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366117</t>
+          <t>366066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720793</t>
+          <t>719599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>738684</t>
+          <t>737974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>17465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>27703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503608</t>
+          <t>504449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516901</t>
+          <t>516751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152390</t>
+          <t>151897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163887</t>
+          <t>163688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>661371</t>
+          <t>660333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>677580</t>
+          <t>678606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>17288</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>38331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23812</t>
+          <t>25378</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48737</t>
+          <t>48112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1111788</t>
+          <t>1111307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1132770</t>
+          <t>1132350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>807927</t>
+          <t>808324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821702</t>
+          <t>821480</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926777</t>
+          <t>1927402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1951702</t>
+          <t>1950136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15705</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36114</t>
+          <t>34904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32026</t>
+          <t>33489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33306</t>
+          <t>32816</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60928</t>
+          <t>61176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>584592</t>
+          <t>585802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>605001</t>
+          <t>604817</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706218</t>
+          <t>704755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724266</t>
+          <t>723908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1298022</t>
+          <t>1297774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1325644</t>
+          <t>1326134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41455</t>
+          <t>42403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31436</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>61158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261800</t>
+          <t>264521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278531</t>
+          <t>279185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1040570</t>
+          <t>1039622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1062326</t>
+          <t>1063174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1309425</t>
+          <t>1308012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1337734</t>
+          <t>1336517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71052</t>
+          <t>71403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108358</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68556</t>
+          <t>71784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108213</t>
+          <t>109264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150940</t>
+          <t>151441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204937</t>
+          <t>205354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3277364</t>
+          <t>3277349</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3314670</t>
+          <t>3314319</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3423383</t>
+          <t>3422332</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3463040</t>
+          <t>3459812</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6712381</t>
+          <t>6711964</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6766378</t>
+          <t>6765877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>493763</t>
+          <t>494394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503210</t>
+          <t>503268</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430065</t>
+          <t>429663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439786</t>
+          <t>439968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927709</t>
+          <t>927370</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941478</t>
+          <t>941386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428316</t>
+          <t>427594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446550</t>
+          <t>446385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>372793</t>
+          <t>373361</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380192</t>
+          <t>380260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>804104</t>
+          <t>806888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824339</t>
+          <t>824970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>25141</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>28363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644444</t>
+          <t>643123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665473</t>
+          <t>663967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157499</t>
+          <t>157320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164281</t>
+          <t>164052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>805317</t>
+          <t>806812</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828434</t>
+          <t>827884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34770</t>
+          <t>34131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29793</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28736</t>
+          <t>28292</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>56846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1000049</t>
+          <t>1000688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019133</t>
+          <t>1019309</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>948301</t>
+          <t>947439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>968450</t>
+          <t>968777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1955337</t>
+          <t>1956066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1984176</t>
+          <t>1984620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>9843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>31565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41039</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64981</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444447</t>
+          <t>443481</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465874</t>
+          <t>465203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>800296</t>
+          <t>799904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>821419</t>
+          <t>821663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1251400</t>
+          <t>1251127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1281941</t>
+          <t>1281958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34854</t>
+          <t>34866</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227633</t>
+          <t>227979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>729872</t>
+          <t>731262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747365</t>
+          <t>747402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>967024</t>
+          <t>967012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>986547</t>
+          <t>986199</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53568</t>
+          <t>50777</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96325</t>
+          <t>93159</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71881</t>
+          <t>70314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109982</t>
+          <t>109521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134999</t>
+          <t>135318</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>191406</t>
+          <t>193373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3279735</t>
+          <t>3282901</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3322492</t>
+          <t>3325283</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3467776</t>
+          <t>3468237</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3505877</t>
+          <t>3507444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6762412</t>
+          <t>6760445</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6818819</t>
+          <t>6818500</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15A-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21244</t>
+          <t>20975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452532</t>
+          <t>452801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>467167</t>
+          <t>467165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290818</t>
+          <t>290837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302909</t>
+          <t>303709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>748005</t>
+          <t>750444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767362</t>
+          <t>767746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>29945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342773</t>
+          <t>344765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>359397</t>
+          <t>359547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359105</t>
+          <t>359913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369818</t>
+          <t>369954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708749</t>
+          <t>708854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>727492</t>
+          <t>727244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40745</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47326</t>
+          <t>47224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501644</t>
+          <t>503070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523483</t>
+          <t>523544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157321</t>
+          <t>156578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166020</t>
+          <t>165849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>662845</t>
+          <t>662947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686691</t>
+          <t>686340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>27663</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53219</t>
+          <t>53948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81119</t>
+          <t>80747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1185115</t>
+          <t>1184386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1210909</t>
+          <t>1210671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>677801</t>
+          <t>677906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697632</t>
+          <t>697697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1871501</t>
+          <t>1871873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903218</t>
+          <t>1903622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21347</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>15355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>48302</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>329208</t>
+          <t>329194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>343817</t>
+          <t>344019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>536498</t>
+          <t>534919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>554352</t>
+          <t>553397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>871464</t>
+          <t>871005</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>894511</t>
+          <t>894150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>25941</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,49 +2463,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>28042</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>19275</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>41154</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>3,3%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>28042</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>40836</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32297</t>
+          <t>32092</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>58262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272128</t>
+          <t>272260</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288352</t>
+          <t>288499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,47 +2576,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>96,75%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1220718</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1207606</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1229485</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>96,7%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1220718</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1207924</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1230397</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1487838</t>
+          <t>1488698</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1514663</t>
+          <t>1514868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>102509</t>
+          <t>101649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146844</t>
+          <t>144964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76539</t>
+          <t>75605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115494</t>
+          <t>114931</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>186866</t>
+          <t>186476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>244476</t>
+          <t>245509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3123346</t>
+          <t>3125226</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3167681</t>
+          <t>3168541</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3262630</t>
+          <t>3263193</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3301585</t>
+          <t>3302519</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6403838</t>
+          <t>6402805</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6461448</t>
+          <t>6461838</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25888</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13676</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35715</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411323</t>
+          <t>412904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429568</t>
+          <t>429352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296192</t>
+          <t>295793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311635</t>
+          <t>310910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>715950</t>
+          <t>716253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737989</t>
+          <t>738295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25561</t>
+          <t>25713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399499</t>
+          <t>398576</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412535</t>
+          <t>412657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327236</t>
+          <t>325768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337040</t>
+          <t>337024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731247</t>
+          <t>731095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747875</t>
+          <t>747936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>27218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>14385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34281</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602616</t>
+          <t>602197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619588</t>
+          <t>619577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247211</t>
+          <t>245739</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258098</t>
+          <t>258114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>855263</t>
+          <t>855241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>874998</t>
+          <t>875159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>50612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,82 +4412,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16816</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10019</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26598</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>51908</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>39833</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>69557</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16816</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9507</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26983</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>51908</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>38157</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>68389</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1109624</t>
+          <t>1108397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134991</t>
+          <t>1133510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,82 +4525,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>749841</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>740059</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>756638</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1873759</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1856110</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1885834</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>97,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>749841</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>739674</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>757150</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1873759</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1857278</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1887510</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22775</t>
+          <t>22424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>54234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>487821</t>
+          <t>488172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502843</t>
+          <t>503635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>723572</t>
+          <t>722930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>743884</t>
+          <t>743820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1218874</t>
+          <t>1217884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1244122</t>
+          <t>1243754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52671</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>32319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253082</t>
+          <t>253778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264001</t>
+          <t>264021</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1056680</t>
+          <t>1057925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1082185</t>
+          <t>1082372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1317631</t>
+          <t>1317053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1342201</t>
+          <t>1343914</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78337</t>
+          <t>79744</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119118</t>
+          <t>119985</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79636</t>
+          <t>78777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121801</t>
+          <t>119075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170310</t>
+          <t>168793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>228484</t>
+          <t>224879</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3302792</t>
+          <t>3301925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3343573</t>
+          <t>3342166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3428324</t>
+          <t>3431050</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3470489</t>
+          <t>3471348</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6743551</t>
+          <t>6747156</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6801725</t>
+          <t>6803242</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>13884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410822</t>
+          <t>410879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424892</t>
+          <t>425141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333363</t>
+          <t>333171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344193</t>
+          <t>344212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>749029</t>
+          <t>749935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766950</t>
+          <t>766878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>364870</t>
+          <t>364498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375250</t>
+          <t>375213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350551</t>
+          <t>351193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366066</t>
+          <t>365986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>719599</t>
+          <t>720923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737974</t>
+          <t>738817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>26298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504449</t>
+          <t>503753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516751</t>
+          <t>516898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151897</t>
+          <t>151638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163688</t>
+          <t>163015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>660333</t>
+          <t>661738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>678606</t>
+          <t>678242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38331</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25378</t>
+          <t>25209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48112</t>
+          <t>47897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1111307</t>
+          <t>1111065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1132350</t>
+          <t>1132702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>808324</t>
+          <t>808527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821480</t>
+          <t>821935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1927402</t>
+          <t>1927617</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1950136</t>
+          <t>1950305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>16073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34904</t>
+          <t>35866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32816</t>
+          <t>33456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61176</t>
+          <t>61021</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>585802</t>
+          <t>584840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>604817</t>
+          <t>604633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>704755</t>
+          <t>704802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>723908</t>
+          <t>723885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1297774</t>
+          <t>1297929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1326134</t>
+          <t>1325494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22624</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,47 +7733,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>29958</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>20106</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>44136</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>29958</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>18851</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>42403</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>31635</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61158</t>
+          <t>60519</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264521</t>
+          <t>263136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279185</t>
+          <t>279174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,47 +7846,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>967</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1052067</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1037889</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1061919</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>97,23%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>967</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1052067</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1039622</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1063174</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1308012</t>
+          <t>1308651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1336517</t>
+          <t>1337535</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71403</t>
+          <t>72284</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>108373</t>
+          <t>110049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71784</t>
+          <t>67355</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109264</t>
+          <t>108799</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>151441</t>
+          <t>150331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>205354</t>
+          <t>202750</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3277349</t>
+          <t>3275673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3314319</t>
+          <t>3313438</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3422332</t>
+          <t>3422797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3459812</t>
+          <t>3464241</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6711964</t>
+          <t>6714568</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6765877</t>
+          <t>6766987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>12367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25309</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500075</t>
+          <t>544554</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>494394</t>
+          <t>538251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503268</t>
+          <t>548429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>435770</t>
+          <t>474073</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429663</t>
+          <t>465761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439968</t>
+          <t>479030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>935845</t>
+          <t>1018628</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927370</t>
+          <t>1010082</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941386</t>
+          <t>1025361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>470439</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427594</t>
+          <t>458447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446385</t>
+          <t>476870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>377498</t>
+          <t>417367</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>373361</t>
+          <t>413505</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>380260</t>
+          <t>420482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>817988</t>
+          <t>887806</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>806888</t>
+          <t>874849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>824970</t>
+          <t>894874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25141</t>
+          <t>23981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17607</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>13147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28363</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>655892</t>
+          <t>456833</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643123</t>
+          <t>447631</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663967</t>
+          <t>463555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>161676</t>
+          <t>181961</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157320</t>
+          <t>177439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164052</t>
+          <t>184894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>817568</t>
+          <t>638794</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>806812</t>
+          <t>627296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827884</t>
+          <t>645962</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>17599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30655</t>
+          <t>31079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>48254</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28292</t>
+          <t>36358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56846</t>
+          <t>64623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1011633</t>
+          <t>1104681</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1000688</t>
+          <t>1093506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019309</t>
+          <t>1114244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>958819</t>
+          <t>840119</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947439</t>
+          <t>830132</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>968777</t>
+          <t>846643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1970451</t>
+          <t>1944800</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1956066</t>
+          <t>1928431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1984620</t>
+          <t>1956696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31565</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41431</t>
+          <t>43760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>46663</t>
+          <t>49043</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34423</t>
+          <t>37089</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65254</t>
+          <t>68116</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>457527</t>
+          <t>549703</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>443481</t>
+          <t>535746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465203</t>
+          <t>558224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>812190</t>
+          <t>800068</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>799904</t>
+          <t>787090</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>821663</t>
+          <t>808231</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1269718</t>
+          <t>1349771</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1251127</t>
+          <t>1330698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1281958</t>
+          <t>1361725</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34866</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>238227</t>
+          <t>234720</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227979</t>
+          <t>223262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>741069</t>
+          <t>823689</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>731262</t>
+          <t>813255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>747402</t>
+          <t>829815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>979296</t>
+          <t>1058409</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>967012</t>
+          <t>1045653</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>986199</t>
+          <t>1065795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>72217</t>
+          <t>81546</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>62592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93159</t>
+          <t>103778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,67 +10726,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>90736</t>
+          <t>98116</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70314</t>
+          <t>83482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109521</t>
+          <t>118874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>179663</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>156166</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>209859</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>162953</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>135318</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>193373</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3303843</t>
+          <t>3360930</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3282901</t>
+          <t>3338698</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3325283</t>
+          <t>3379884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,67 +10839,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3487022</t>
+          <t>3537277</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3468237</t>
+          <t>3516519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3507444</t>
+          <t>3551911</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>8310</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6898206</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6868010</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6921703</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>97,46%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>8310</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6790865</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6760445</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6818500</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
